--- a/Coimbatore-March-2026.xlsx
+++ b/Coimbatore-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Sr. No</t>
   </si>
@@ -109,19 +109,16 @@
     <t>TN09DF3647</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Etios</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>ETIOS</t>
   </si>
   <si>
     <t>29/01/2020</t>
   </si>
   <si>
     <t>24/05/2019</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -742,7 +739,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>10229</v>
